--- a/land-jv-research/data/land_jv_usa_research.xlsx
+++ b/land-jv-research/data/land_jv_usa_research.xlsx
@@ -12,9 +12,16 @@
     <sheet name="2. Реклама (измерено)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. SEC Form D" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="4. Модель бюджета (оценка)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5. Каналы" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5. Бюджет по каналам" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="6. Доказательства" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="7. Бенчмарк-панель" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8. Каналы продвижения" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9. Языки и регионы" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10. Инструменты" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11. Разбор воронок" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12. Крупный чек" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13. Конференции 2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14. Города" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -108,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -134,6 +141,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -686,7 +696,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'5. Каналы'!B4</f>
+              <f>'5. Бюджет по каналам'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -696,17 +706,99 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'5. Каналы'!$A$5:$A$12</f>
+              <f>'5. Бюджет по каналам'!$A$5:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'5. Каналы'!$B$5:$B$12</f>
+              <f>'5. Бюджет по каналам'!$B$5:$B$12</f>
             </numRef>
           </val>
         </ser>
         <firstSliceAng val="0"/>
       </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Компаний двадцатки по метрополиям</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'14. Города'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'14. Города'!$A$5:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'14. Города'!$B$5:$B$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -835,6 +927,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1557,6 +1676,2402 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ЯЗЫКИ И РЕГИОНЫ ПРОДВИЖЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Компания</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Языки</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Региональные порталы</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Офисы</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Регионы</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Активность 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Walton Global</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EN, 繁體中文, 简体中文, 日本語, DEUTSCH (5 языков)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Asia &amp; Middle East, Canada, Germany, VISTRA, Great Lakes</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Scottsdale, Calgary, Гонконг, Тайбэй, Сингапур, Манила, Токио, Дубай</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>91 страна. Фокус: Азия, Ближний Восток, Европа</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Япония: фонд "US My Home Fund", запуск в Токио 10.04.2026, дистрибьюторы Teneo Partners и Matsuzaka Securities. Тайбэй: роудшоу. Гонконг: зарегистрированный инвестиционный инструмент. U.S. Land Income &amp; Growth Fund для офшорных инвесторов, первое закрытие 10.2025. PR-синдикация через BERNAMA (Малайзия), ANTARA (Индонезия), Japan Times, индийские издания.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Millrose Properties</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Майами</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>США, 30 штатов</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Публичный REIT, капитал с биржи. Языковых версий нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DLP Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>St. Augustine, FL</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>США, одобрен к кредитованию в 37 штатах</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Вебинары, Elite Impact Podcast, Investor Vision Day. Только английский, только США.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Caliber (NASDAQ: CWD)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>США, Юго-Запад</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5 соцканалов — максимум выборки. Цели 2024-2026: привлечь $750 млн, AUM $3 млрд.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MLG Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Brookfield, WI</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>США: Southeast, Mountain West, Midwest</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4 соцканала. Дистрибуция через investment advisors и family offices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AcreTrader</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>США, сельхозземля</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Контент-воронка: 152 видео. 100% предложений 506(c).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FarmTogether</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Сан-Франциско</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>США, permanent crops</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4 соцканала, ~1 новое предложение в месяц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Прочие 13 компаний топ-20</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>EN (только английский)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>США, преимущественно Солнечный пояс</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ни у одной нет языковых версий сайта, региональных порталов или зарубежной дистрибуции.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ОТДЕЛЬНЫЙ КАНАЛ ИНОСТРАННОГО КАПИТАЛА: EB-5 (иммиграционные инвестиции)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Что это</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Иностранный инвестор вкладывает $800 тыс.–$1,05 млн в проект США и получает путь к грин-карте. Девелопмент и земля — один из основных классов проектов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Зачем смотреть</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Это параллельный канал привлечения капитала под крупные чеки, работающий на других языках и в других регионах, чем внутренний рынок США.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>География</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Китай 56,3% заявителей, затем Индия и Вьетнам — вместе более 75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Примеры</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CanAm Enterprises: штаб-квартира Нью-Йорк, офисы в Пекине, Шанхае, Хошимине, Нью-Дели, Сингапуре. EB5AN: 3 000+ инвесторов из 70+ стран, $1 млрд капитала, $8 млрд стоимости проектов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Механика</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Привлечение идёт через миграционных агентов за комиссию, а не через рекламу. Отраслевое медиа — EB5Investors Magazine. Материалы обязательно переводятся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Оговорка</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Ни одна из 20 компаний основного рейтинга не использует EB-5 как заявленный канал. Включено как отдельная возможность, а не как наблюдаемая практика выборки.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>СТАТУС ИНСТРУМЕНТОВ ИЗМЕРЕНИЯ — каждый проверен контрольным запросом</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Контрольный запрос обязан вернуть много. Если инструмент возвращает ноль на Nike — его нули ничего не значат и в выводы не идут.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Контрольный запрос</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Что покрывает</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="7" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>ВАЛИДЕН</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fundrise.com -&gt; 200+ объявлений</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Поиск Google, YouTube, Display, Shopping</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Показывает наличие и количество объявлений. Суммы НЕ показывает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Meta Ad Library</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>ВАЛИДЕН</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nike -&gt; 24 000 результатов</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Facebook, Instagram, Messenger, Audience Network</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Поиск по тексту объявления. Компания, не упоминающая себя в тексте, может быть недосчитана. Суммы для неполитической рекламы НЕ показывает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TikTok Commercial Content Library</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>НЕ ВАЛИДЕН</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nike, Temu, Shopify, Samsung -&gt; все 0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Фильтр страны не устанавливается, библиотека возвращает нули на заведомо крупных рекламодателей. Результаты по TikTok в выводы НЕ включены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LinkedIn Ad Library</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>НЕДОСТУПЕН</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cloudflare блокирует доступ. Присутствие на LinkedIn снято по ссылкам с сайтов компаний, объёма рекламы нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>X / Twitter</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>НЕДОСТУПЕН</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Публичного репозитория рекламы для США нет (DSA-репозиторий покрывает только ЕС).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Сайты компаний</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>ВАЛИДЕН</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>снято с 20 из 20 сайтов</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Наличие каналов, языковые версии</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Прямой разбор DOM: ссылки на соцсети, hreflang, языковые переключатели.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>СЛЕПОК ВОРОНКИ: куда ведут трафик и чем цепляют</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Пиксель на сайте = канал реально используется. Это точнее рекламных библиотек: библиотека может не показать объявления, но пиксель стоит только у того, кто льёт трафик.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Компания</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Заголовок страницы</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>CTA (призывы)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Поля формы (что спрашивают у лида)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Спрашивают аккредитацию</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Платные каналы по пикселям</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Платных каналов, шт</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>CRM / автоматизация</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>UX-аналитика</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Трекеров всего</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Caliber</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.caliberco.com/</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SEC Accredited Investor definition | LEARN MORE | Public Investors (CWD) | Opportunity Zone Investing | OFFERINGS &amp; ASSETS | Investor Resources | Invest in Arizona | Invest in Colorado</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>firstname, lastname, email, phone, is_accredited, is_financial_professional, g-recaptcha-response, hs_context, s</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, LinkedIn Insight, TikTok Pixel, X Pixel, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fundrise</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://fundrise.com/</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Invest in a better alternative</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Enable accessibility for low vision | Open the accessibility menu | Get started | Learn more | Explore our real estate portfolio | Explore our private credit portfolio | Learn more about VCX | Invest in your retirement</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, LinkedIn Insight, X Pixel, Microsoft/Bing UET, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MLG Capital</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://mlgcapital.com/invest/</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Error 404</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Investing | Investment Advisors | Joint Venture Partnership | Our Portfolio | Investor Portal | GET STARTED | Ways to Invest With MLG | Get Started</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>s, ak_hp_textarea, ak_js, input_31, input_3, input_25, input_26, input_27, input_28, input_29, gform_ajax, gform_submission_method</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, LinkedIn Insight, Microsoft/Bing UET, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>HubSpot, Pardot</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Hotjar, MS Clarity</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DLP Capital</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://dlpcapital.com/invest</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Housing for America’s families &amp; financial legacies for yours.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Invest | DLP Lending Fund Series B Note Offering | DLP Preferred Credit Fund Series A Note Offering | Investor Login | Webinars | Get Started | Learn More | Browse Webinars</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>firstname, lastname, last_form_phone_number, email, what_s_your_interest_in_dlp_capital, are_you_a_credited_investor_, interest, message, ip_address, hs_context, company, gated_content</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, LinkedIn Insight, Microsoft/Bing UET, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Hotjar</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DLP вебинары</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://dlpcapital.com/twenty/webinars</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Webinars</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Invest | DLP Lending Fund Series B Note Offering | DLP Preferred Credit Fund Series A Note Offering | Investor Login | Webinars | Get Started | Learn More | Browse Webinars</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>twenty-category, email, hs_context, firstname, lastname, what_s_your_interest_in_dlp_capital, are_you_a_credited_investor_, company, last_form_phone_number, gated_content, ip_address, investor_record</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, LinkedIn Insight, Microsoft/Bing UET, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hotjar</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Origin Investments</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://origininvestments.com/</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Origin’s strategies are organized around three investor priorities: generating income, driving long-term growth, and managing the impact of taxes.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Get Started | Investments | All Investments | Investment Strategy | Investing Fundamentals | Investing Education | Investing with Origin | Fund Webinars</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>checkbox, s</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, LinkedIn Insight, Microsoft/Bing UET, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Marketo</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MS Clarity</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cardone Capital</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://cardonecapital.com/</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Best in Class Real Estate Made Available to Everyday Investors</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Investments | Invest Now | Get Started | Real Estate Portfolio → | Explore Real Estate Portfolio → | Learn More | Facebook | Free Books</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>g-recaptcha-response</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, TikTok Pixel, X Pixel, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AcreTrader</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://acretrader.com/</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Farmland Investing. Simplified.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Invest | Sign Up | Get Started | Learn More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>enter your email address, email address</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Allied Development</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://alliedlandfund.com/</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>A REAL ESTATE FUND DESIGNED TO PAY INVESTORS FIRST</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>GET INVESTOR INFORMATION</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Meta Pixel, Google Ads remarketing</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Walton Global</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://walton.com/contact-capital-markets/</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>WALTON INVESTMENT PORTAL</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>INVESTMENTS | Investments | Investments Overview | Pre-Development Land Investment | DST / 1031 Growth Investments</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>s, et_pb_searchform_submit, et_pb_include_posts, et_pb_include_pages, input_2.3, input_2.6, input_3, input_22, input_25, input_13, input_24, g-recaptcha-response</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ — платных каналов не ведёт</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Hotjar</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FarmTogether</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://farmtogether.com/</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Customize your cookie preferences</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Considering a 1031 Exchange? Learn More | INVEST | SIGN UP | GET STARTED | LIVE OFFERINGS | SEE OUR PORTFOLIO | LEARN MORE | DOWNLOAD WHITE PAPER</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ — платных каналов не ведёт</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GSP REI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://gsprei.com/land-entitlement-fund/</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>THE EDGE THAT SETS US APART</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Investment Approach | Invest With Us | Investor Login | Join the Waitlist | Land Offering | Income Fund Offering | Invest Now | Schedule a Call with Management</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>enter your email</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ — платных каналов не ведёт</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="88" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ЭКОНОМИКА КАНАЛА $1 МЛН+ — выбранный сегмент</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Это каналы, которыми пользуются Walton, Crow, Domain и Bedrock. Ни один из них не виден в рекламных библиотеках, потому что это не реклама.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>СЦЕНАРИЙ</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Логика расчёта</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Стоимость</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Вердикт</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Обоснование</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Платный цифровой трафик под чек $1 млн+</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CPL аккредитованного инвестора $50–500; стоимость профинансировавшего инвестора $3 500–4 500. Для $20 млн нужно ~20 инвесторов по $1 млн.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>~$90 000 (20 × $4 500)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>НЕ РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Бенчмарк $3 500–4 500 получен на чеках $100–200 тыс. Конверсия холодного цифрового лида в чек $1 млн близка к нулю: такие решения не принимаются по клику. Доказательство: у Walton ($8,28 млрд) и Crow ($38,2 млрд, медианный чек $5 млн) — ноль объявлений и ни одного рекламного пикселя на сайте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Placement agent</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1,5–2,5% success fee плюс ретейнер $10–25 тыс./мес на 6–18 мес.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>$500 000 (2,5%) + ретейнер $60–300 тыс.</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>РАБОТАЕТ, но дорого</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Платите за готовый доступ к LP. Агент обязан быть зарегистрирован в FINRA. Полная стоимость привлечения со всеми издержками — 4–8% от эквити.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Собственная сеть дистрибьюторов</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Модель Walton: 300+ одобренных каналов — брокер-дилеры, RIA, family offices.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5–8% от привлечённого, но платится по факту</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>РАБОТАЕТ, масштабируется</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Дороже агента в процентах, но строит собственный актив, а не арендует чужой. Walton собрал так 89 000 инвесторов из 91 страны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Конференц-цикл</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>10 профильных событий в год по $3–7,5 тыс. за вход плюс перелёты и представительские.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>$30–75 тыс. вход + $50–100 тыс. сопутствующие</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>РАБОТАЕТ как вход в канал</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Самый дешёвый способ физически попасть к family offices. Экономика событий устроена так, что инвесторы от $100 млн проходят бесплатно, а платит ищущий деньги — то есть организатор гарантирует вам нужную аудиторию в зале.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>РАСЦЕНКИ PLACEMENT AGENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Success fee, фонд до $100 млн</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2,0–2,5% от привлечённого</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pipelineroad.com/blog/placement-agent-fees-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Success fee, фонд $100–500 млн</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1,5–2,0%</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pipelineroad.com/blog/placement-agent-fees-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Success fee, фонд свыше $500 млн</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1,0–1,5%</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pipelineroad.com/blog/placement-agent-fees-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Success fee, недвижимость (отраслевой диапазон)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1–3% от привлечённого эквити</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>selltohomepros.com/blog/real-estate-fund-placement-explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ретейнер разовый</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>$25 000 – $100 000+</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pipelineroad.com/blog/placement-agent-fees-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ретейнер ежемесячный</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$10 000 – $25 000/мес</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lpbacked.com/resources/placement-agent-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Период эксклюзивности</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6–18 месяцев</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lpbacked.com/resources/placement-agent-fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Требование к агенту</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Регистрация FINRA, Series 7/79</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>selltohomepros.com/blog/real-estate-fund-placement-explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ПОЛНАЯ стоимость привлечения (все издержки)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4–8% от привлечённого эквити</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>accreditedinvestorleadgeneration.com/capital-raising/real-cost-raising-capital-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Пример: фонд $250 млн при ставке 1,75%</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$4 375 000 только агенту</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pipelineroad.com/blog/placement-agent-fees-2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ГДЕ ФИЗИЧЕСКИ НАХОДЯТСЯ ДЕНЬГИ: профильные события 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Экономика этих событий устроена в вашу пользу наоборот: инвесторы от $100 млн проходят бесплатно, платит тот, кто ищет капитал. Организатор гарантирует нужную аудиторию в зале.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Когда</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Где</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Цена входа для управляющего</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Opal Family Office Winter Forum</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>New York Marriott Marquis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>$2 895</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Семейные офисы от $100 млн проходят бесплатно — платит тот, кто ищет деньги</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Opal Family Office &amp; Private Wealth Management Forum</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>27–29.07.2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Newport, RI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>$3 195 early / $3 495 standard</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Три дня, основной летний слёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Opal Family Office &amp; Private Wealth Legacy Summit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08.2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>$3 195</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Верифицированные family offices от $100 млн — бесплатно</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Markets Group Private Wealth US Spring Retreat</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>11–13.05.2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>$7 500</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Самый дорогой вход в выборке; квалифицированные инвесторы бесплатно</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IMN Real Estate Family Office &amp; Private Wealth East</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>26–27.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Loews Coral Gables, FL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>уточняется у организатора</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Профильный для недвижимости, Майами</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IMN Real Estate Private Funds</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>24–26.06.2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Newport, RI</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>уточняется у организатора</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Фонды недвижимости и их LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IMN Land &amp; Homebuilding Capital Markets</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01–02.06.2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>уточняется у организатора</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ЕДИНСТВЕННОЕ профильное событие именно по земле и жилью</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Opal Real Estate Investment Summit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>04.2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Флорида</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>уточняется у организатора</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Недвижимость, Флорида</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>РАЗРЕЗ ПО ГОРОДАМ: где сидят игроки двадцатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Нью-Йорка в этом рынке нет: ни одна компания двадцатки там не базируется. Рынок земли сконцентрирован в Солнечном поясе, где есть пригодная к застройке земля.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Метрополия</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Компаний</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Сумма объявлений Google</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Компании</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Финикс / Скоттсдейл, AZ</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Walton Global, Caliber (NASDAQ: CWD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Майами, FL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Millrose Properties (NYSE: MRP), 13th Floor Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Даллас, TX</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Crow Holdings, Bedrock Land Finance (TWG Global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Даллас–Форт-Уэрт, TX</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Forestar Group (NYSE: FOR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Сан-Франциско, CA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>FarmTogether</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Милуоки, WI</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MLG Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Джэксонвилл, FL</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>DLP Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>не раскрыто</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Allied Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Арканзас</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>AcreTrader</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Сан-Хосе, CA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Urban Catalyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Хьюстон, TX</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Howard Hughes Holdings (NYSE: HHH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Панхандл Флориды</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>The St. Joe Company (NYSE: JOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Филадельфия, PA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>GSP REI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Чикаго, IL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Domain Real Estate Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Майами / Форт-Лодердейл, FL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>BTI Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Лос-Анджелес, CA</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Tejon Ranch Co (NYSE: TRC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ориндж-Каунти, CA</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Five Point Holdings (NYSE: FPH)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -17580,4 +20095,1189 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>КАНАЛЫ ПРОДВИЖЕНИЯ: что измерено по каждой компании</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Google и Meta — количество активных объявлений. Соцсети — наличие канала по ссылкам с сайта. Суммы расходов не раскрывает ни одна из платформ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Компания</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Google объявлений (изм.)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Meta объявлений (изм.)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Meta: достоверность</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>X/Twitter</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Каналов всего</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Языковых версий сайта</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="7" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Caliber</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>не снято</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GSP REI</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ноль, но возможен ложный ноль (см. New Western)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BTI Partners</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>не снято</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FarmTogether</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>27000</v>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>НЕДОСТОВЕРНО: имя из общих слов, матчится чужая реклама</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MLG Capital</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>ноль, но возможен ложный ноль (см. New Western)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>St. Joe</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>НЕДОСТОВЕРНО: имя из общих слов, матчится чужая реклама</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AcreTrader</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>достоверно: редкое имя</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tejon Ranch</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>НЕДОСТОВЕРНО: имя из общих слов, матчится чужая реклама</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Urban Catalyst</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>достоверно: редкое имя</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Howard Hughes</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>ноль, но возможен ложный ноль (см. New Western)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13th Floor</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>достоверно: редкое имя</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Crow Holdings</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ноль, но возможен ложный ноль (см. New Western)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Domain REP</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ноль, но возможен ложный ноль (см. New Western)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Forestar</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>НЕДОСТОВЕРНО: имя из общих слов, матчится чужая реклама</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Walton Global</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ноль, но возможен ложный ноль (см. New Western)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Allied Development</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>НЕДОСТОВЕРНО: имя из общих слов, матчится чужая реклама</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bedrock Land Finance</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>достоверно: редкое имя</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DLP Capital</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>достоверно: редкое имя</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Five Point</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>НЕДОСТОВЕРНО: имя из общих слов, матчится чужая реклама</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Millrose Properties</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ноль, но возможен ложный ноль (см. New Western)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>